--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20261012.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20261012.xlsx
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>88,368,399</t>
+          <t>45,282,484</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>45,282,484</t>
+          <t>88,368,399</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
